--- a/data/sims/109_2025_full_table_sim.xlsx
+++ b/data/sims/109_2025_full_table_sim.xlsx
@@ -28,40 +28,40 @@
     <t>Top 4</t>
   </si>
   <si>
+    <t>Unia Skierniewice</t>
+  </si>
+  <si>
     <t>Warta Poznań</t>
   </si>
   <si>
-    <t>Unia Skierniewice</t>
-  </si>
-  <si>
     <t>Olimpia Grudziądz</t>
   </si>
   <si>
     <t>Podhale Nowy Targ</t>
   </si>
   <si>
+    <t>Świt Skolwin</t>
+  </si>
+  <si>
     <t>Stal Stalowa Wola</t>
   </si>
   <si>
-    <t>Świt Skolwin</t>
-  </si>
-  <si>
     <t>Chojniczanka Chojnice</t>
   </si>
   <si>
+    <t>Resovia Rzeszów</t>
+  </si>
+  <si>
+    <t>Podbeskidzie</t>
+  </si>
+  <si>
+    <t>Sandecja Nowy Sącz</t>
+  </si>
+  <si>
     <t>Zaglebie Sosnowiec</t>
   </si>
   <si>
-    <t>Resovia Rzeszów</t>
-  </si>
-  <si>
-    <t>Sandecja Nowy Sącz</t>
-  </si>
-  <si>
     <t>Śląsk Wrocław II</t>
-  </si>
-  <si>
-    <t>Podbeskidzie</t>
   </si>
   <si>
     <t>Sokół Kleczew</t>
@@ -513,34 +513,34 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>1076.44</v>
+        <v>1066.29</v>
       </c>
       <c r="C2">
-        <v>65.13</v>
+        <v>64.36</v>
       </c>
       <c r="D2">
-        <v>97.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="E2">
-        <v>59</v>
+        <v>50.8</v>
       </c>
       <c r="F2">
-        <v>24.7</v>
+        <v>30.9</v>
       </c>
       <c r="G2">
-        <v>10.5</v>
+        <v>11.4</v>
       </c>
       <c r="H2">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I2">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J2">
         <v>0.5</v>
       </c>
       <c r="K2">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L2">
         <v>0.1</v>
@@ -581,49 +581,49 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>1036.53</v>
+        <v>1102.42</v>
       </c>
       <c r="C3">
-        <v>61.06</v>
+        <v>63.02</v>
       </c>
       <c r="D3">
-        <v>89.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E3">
-        <v>23.6</v>
+        <v>37.4</v>
       </c>
       <c r="F3">
-        <v>33.4</v>
+        <v>35.9</v>
       </c>
       <c r="G3">
-        <v>22.3</v>
+        <v>15.6</v>
       </c>
       <c r="H3">
-        <v>9.9</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J3">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="L3">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="M3">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="N3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -649,49 +649,49 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>1036.53</v>
+        <v>1066.29</v>
       </c>
       <c r="C4">
-        <v>59.17</v>
+        <v>56.92</v>
       </c>
       <c r="D4">
-        <v>82.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E4">
-        <v>13.9</v>
+        <v>6.3</v>
       </c>
       <c r="F4">
-        <v>26.9</v>
+        <v>15.8</v>
       </c>
       <c r="G4">
-        <v>28.3</v>
+        <v>27.8</v>
       </c>
       <c r="H4">
-        <v>13.8</v>
+        <v>22</v>
       </c>
       <c r="I4">
-        <v>7.5</v>
+        <v>12.4</v>
       </c>
       <c r="J4">
-        <v>4.1</v>
+        <v>6.7</v>
       </c>
       <c r="K4">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="M4">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="N4">
+        <v>0.7</v>
+      </c>
+      <c r="O4">
         <v>0.5</v>
       </c>
-      <c r="O4">
-        <v>0.3</v>
-      </c>
       <c r="P4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q4">
         <v>0.1</v>
@@ -717,61 +717,61 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>986.65</v>
+        <v>1021.13</v>
       </c>
       <c r="C5">
-        <v>52.3</v>
+        <v>55.15</v>
       </c>
       <c r="D5">
-        <v>35.7</v>
+        <v>57.6</v>
       </c>
       <c r="E5">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="F5">
-        <v>5.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G5">
-        <v>11.4</v>
+        <v>21.5</v>
       </c>
       <c r="H5">
-        <v>17.6</v>
+        <v>22.6</v>
       </c>
       <c r="I5">
-        <v>14.5</v>
+        <v>15.9</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="L5">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="M5">
-        <v>5.8</v>
+        <v>2.7</v>
       </c>
       <c r="N5">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="P5">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="Q5">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="R5">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="S5">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -785,61 +785,61 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1024.06</v>
+        <v>1030.16</v>
       </c>
       <c r="C6">
-        <v>50.43</v>
+        <v>52.68</v>
       </c>
       <c r="D6">
-        <v>23.1</v>
+        <v>36.6</v>
       </c>
       <c r="E6">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="G6">
-        <v>6.7</v>
+        <v>12.6</v>
       </c>
       <c r="H6">
-        <v>12.6</v>
+        <v>17.4</v>
       </c>
       <c r="I6">
-        <v>13.5</v>
+        <v>18.8</v>
       </c>
       <c r="J6">
-        <v>12.4</v>
+        <v>13.7</v>
       </c>
       <c r="K6">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
       <c r="L6">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="M6">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="N6">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="Q6">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="R6">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="S6">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="T6">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -853,64 +853,64 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>996.62</v>
+        <v>1055</v>
       </c>
       <c r="C7">
-        <v>49.87</v>
+        <v>48.2</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>10.9</v>
       </c>
       <c r="E7">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F7">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
         <v>6.9</v>
       </c>
-      <c r="H7">
-        <v>11.4</v>
-      </c>
       <c r="I7">
-        <v>12</v>
+        <v>10.6</v>
       </c>
       <c r="J7">
-        <v>12.2</v>
+        <v>12.9</v>
       </c>
       <c r="K7">
-        <v>10.6</v>
+        <v>12.9</v>
       </c>
       <c r="L7">
-        <v>9.300000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="M7">
-        <v>8.199999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="N7">
+        <v>9</v>
+      </c>
+      <c r="O7">
         <v>7.1</v>
       </c>
-      <c r="O7">
-        <v>6</v>
-      </c>
       <c r="P7">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="Q7">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R7">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="S7">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="T7">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -921,64 +921,64 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>1029.05</v>
+        <v>1059.52</v>
       </c>
       <c r="C8">
-        <v>47.1</v>
+        <v>46.93</v>
       </c>
       <c r="D8">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F8">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G8">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="H8">
+        <v>4.6</v>
+      </c>
+      <c r="I8">
+        <v>7.9</v>
+      </c>
+      <c r="J8">
+        <v>10.8</v>
+      </c>
+      <c r="K8">
+        <v>11.1</v>
+      </c>
+      <c r="L8">
+        <v>11.3</v>
+      </c>
+      <c r="M8">
+        <v>10.9</v>
+      </c>
+      <c r="N8">
+        <v>10.1</v>
+      </c>
+      <c r="O8">
+        <v>8.6</v>
+      </c>
+      <c r="P8">
+        <v>7.4</v>
+      </c>
+      <c r="Q8">
         <v>5.7</v>
       </c>
-      <c r="I8">
-        <v>7.8</v>
-      </c>
-      <c r="J8">
-        <v>8.9</v>
-      </c>
-      <c r="K8">
-        <v>9.5</v>
-      </c>
-      <c r="L8">
-        <v>9.6</v>
-      </c>
-      <c r="M8">
-        <v>9.5</v>
-      </c>
-      <c r="N8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="O8">
-        <v>9.1</v>
-      </c>
-      <c r="P8">
-        <v>7.9</v>
-      </c>
-      <c r="Q8">
-        <v>7.3</v>
-      </c>
       <c r="R8">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="S8">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="T8">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="U8">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -989,64 +989,64 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>966.6900000000001</v>
+        <v>1041.45</v>
       </c>
       <c r="C9">
-        <v>47.09</v>
+        <v>46.75</v>
       </c>
       <c r="D9">
-        <v>9.5</v>
+        <v>6.4</v>
       </c>
       <c r="E9">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G9">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="I9">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
-        <v>9.1</v>
+        <v>9.9</v>
       </c>
       <c r="K9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L9">
-        <v>9.800000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="M9">
-        <v>9.5</v>
+        <v>10.9</v>
       </c>
       <c r="N9">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="O9">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="P9">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="Q9">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="R9">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="S9">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="U9">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -1057,64 +1057,64 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>1009.09</v>
+        <v>1023.39</v>
       </c>
       <c r="C10">
-        <v>46.88</v>
+        <v>45.6</v>
       </c>
       <c r="D10">
-        <v>8.5</v>
+        <v>4.3</v>
       </c>
       <c r="E10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="G10">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="H10">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="J10">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="K10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L10">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>9.800000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="N10">
-        <v>9.300000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="O10">
-        <v>8.6</v>
+        <v>10.4</v>
       </c>
       <c r="P10">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Q10">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="R10">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="S10">
         <v>4.3</v>
       </c>
       <c r="T10">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U10">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -1125,64 +1125,64 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>961.7</v>
+        <v>998.55</v>
       </c>
       <c r="C11">
-        <v>46.47</v>
+        <v>44.8</v>
       </c>
       <c r="D11">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="E11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="G11">
+        <v>0.9</v>
+      </c>
+      <c r="H11">
         <v>2.3</v>
       </c>
-      <c r="H11">
-        <v>4.7</v>
-      </c>
       <c r="I11">
+        <v>4.4</v>
+      </c>
+      <c r="J11">
         <v>6.7</v>
       </c>
-      <c r="J11">
-        <v>8</v>
-      </c>
       <c r="K11">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L11">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="M11">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="N11">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="O11">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="P11">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="Q11">
-        <v>7.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="R11">
-        <v>7.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S11">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="T11">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U11">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -1193,64 +1193,64 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>976.67</v>
+        <v>1003.07</v>
       </c>
       <c r="C12">
-        <v>45.75</v>
+        <v>44.34</v>
       </c>
       <c r="D12">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="E12">
         <v>0.1</v>
       </c>
       <c r="F12">
+        <v>0.2</v>
+      </c>
+      <c r="G12">
+        <v>0.8</v>
+      </c>
+      <c r="H12">
+        <v>2.3</v>
+      </c>
+      <c r="I12">
+        <v>3.9</v>
+      </c>
+      <c r="J12">
+        <v>6.3</v>
+      </c>
+      <c r="K12">
+        <v>7.1</v>
+      </c>
+      <c r="L12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M12">
+        <v>9.9</v>
+      </c>
+      <c r="N12">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="O12">
+        <v>10</v>
+      </c>
+      <c r="P12">
+        <v>10.8</v>
+      </c>
+      <c r="Q12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="R12">
+        <v>9.1</v>
+      </c>
+      <c r="S12">
+        <v>6.9</v>
+      </c>
+      <c r="T12">
+        <v>4.2</v>
+      </c>
+      <c r="U12">
         <v>0.6</v>
-      </c>
-      <c r="G12">
-        <v>1.8</v>
-      </c>
-      <c r="H12">
-        <v>3.7</v>
-      </c>
-      <c r="I12">
-        <v>5.8</v>
-      </c>
-      <c r="J12">
-        <v>6.8</v>
-      </c>
-      <c r="K12">
-        <v>8.1</v>
-      </c>
-      <c r="L12">
-        <v>9</v>
-      </c>
-      <c r="M12">
-        <v>9.4</v>
-      </c>
-      <c r="N12">
-        <v>9.4</v>
-      </c>
-      <c r="O12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="P12">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Q12">
-        <v>8.5</v>
-      </c>
-      <c r="R12">
-        <v>7.5</v>
-      </c>
-      <c r="S12">
-        <v>6.1</v>
-      </c>
-      <c r="T12">
-        <v>3.7</v>
-      </c>
-      <c r="U12">
-        <v>0.4</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -1261,67 +1261,67 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>989.14</v>
+        <v>1012.1</v>
       </c>
       <c r="C13">
-        <v>44.38</v>
+        <v>44</v>
       </c>
       <c r="D13">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H13">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="I13">
+        <v>3.4</v>
+      </c>
+      <c r="J13">
+        <v>5.6</v>
+      </c>
+      <c r="K13">
+        <v>6.8</v>
+      </c>
+      <c r="L13">
+        <v>8.6</v>
+      </c>
+      <c r="M13">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="N13">
+        <v>10.3</v>
+      </c>
+      <c r="O13">
+        <v>10.5</v>
+      </c>
+      <c r="P13">
+        <v>10.3</v>
+      </c>
+      <c r="Q13">
+        <v>11.1</v>
+      </c>
+      <c r="R13">
+        <v>9.4</v>
+      </c>
+      <c r="S13">
+        <v>7.5</v>
+      </c>
+      <c r="T13">
         <v>4</v>
-      </c>
-      <c r="J13">
-        <v>5.1</v>
-      </c>
-      <c r="K13">
-        <v>6.1</v>
-      </c>
-      <c r="L13">
-        <v>7.4</v>
-      </c>
-      <c r="M13">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="N13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="O13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="P13">
-        <v>9.9</v>
-      </c>
-      <c r="Q13">
-        <v>10.8</v>
-      </c>
-      <c r="R13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="S13">
-        <v>8.9</v>
-      </c>
-      <c r="T13">
-        <v>6</v>
       </c>
       <c r="U13">
         <v>0.7</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1329,67 +1329,67 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>971.6799999999999</v>
+        <v>1007.58</v>
       </c>
       <c r="C14">
-        <v>43.22</v>
+        <v>43.68</v>
       </c>
       <c r="D14">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G14">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H14">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I14">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J14">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="K14">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="L14">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="M14">
-        <v>7.3</v>
+        <v>9</v>
       </c>
       <c r="N14">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O14">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="P14">
+        <v>10.8</v>
+      </c>
+      <c r="Q14">
+        <v>11.1</v>
+      </c>
+      <c r="R14">
         <v>10.4</v>
       </c>
-      <c r="Q14">
-        <v>10.9</v>
-      </c>
-      <c r="R14">
-        <v>11.4</v>
-      </c>
       <c r="S14">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="T14">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="U14">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="V14">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1397,46 +1397,46 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>956.71</v>
+        <v>994.03</v>
       </c>
       <c r="C15">
-        <v>42.59</v>
+        <v>40.08</v>
       </c>
       <c r="D15">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="H15">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="I15">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J15">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="K15">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="M15">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="N15">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
       <c r="O15">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="P15">
         <v>10.2</v>
@@ -1445,19 +1445,19 @@
         <v>12.2</v>
       </c>
       <c r="R15">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="S15">
-        <v>12.9</v>
+        <v>17.2</v>
       </c>
       <c r="T15">
-        <v>10.3</v>
+        <v>15.8</v>
       </c>
       <c r="U15">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="V15">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1465,67 +1465,67 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>949.23</v>
+        <v>987.26</v>
       </c>
       <c r="C16">
-        <v>39.48</v>
+        <v>39.6</v>
       </c>
       <c r="D16">
+        <v>0.2</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0.2</v>
+      </c>
+      <c r="I16">
+        <v>0.6</v>
+      </c>
+      <c r="J16">
+        <v>1.3</v>
+      </c>
+      <c r="K16">
+        <v>2.1</v>
+      </c>
+      <c r="L16">
+        <v>3.1</v>
+      </c>
+      <c r="M16">
+        <v>4</v>
+      </c>
+      <c r="N16">
+        <v>5.2</v>
+      </c>
+      <c r="O16">
+        <v>7.5</v>
+      </c>
+      <c r="P16">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Q16">
+        <v>11.6</v>
+      </c>
+      <c r="R16">
+        <v>14.6</v>
+      </c>
+      <c r="S16">
+        <v>17.4</v>
+      </c>
+      <c r="T16">
+        <v>18.6</v>
+      </c>
+      <c r="U16">
+        <v>4.1</v>
+      </c>
+      <c r="V16">
         <v>0.4</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0.1</v>
-      </c>
-      <c r="H16">
-        <v>0.3</v>
-      </c>
-      <c r="I16">
-        <v>0.9</v>
-      </c>
-      <c r="J16">
-        <v>1.4</v>
-      </c>
-      <c r="K16">
-        <v>1.8</v>
-      </c>
-      <c r="L16">
-        <v>2.5</v>
-      </c>
-      <c r="M16">
-        <v>3.3</v>
-      </c>
-      <c r="N16">
-        <v>4.7</v>
-      </c>
-      <c r="O16">
-        <v>5.9</v>
-      </c>
-      <c r="P16">
-        <v>8</v>
-      </c>
-      <c r="Q16">
-        <v>9.9</v>
-      </c>
-      <c r="R16">
-        <v>13.7</v>
-      </c>
-      <c r="S16">
-        <v>18.7</v>
-      </c>
-      <c r="T16">
-        <v>23.5</v>
-      </c>
-      <c r="U16">
-        <v>4.8</v>
-      </c>
-      <c r="V16">
-        <v>0.6</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1533,67 +1533,67 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>949.23</v>
+        <v>987.26</v>
       </c>
       <c r="C17">
-        <v>39.17</v>
+        <v>37.64</v>
       </c>
       <c r="D17">
+        <v>0.1</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0.1</v>
+      </c>
+      <c r="I17">
+        <v>0.2</v>
+      </c>
+      <c r="J17">
         <v>0.5</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0.1</v>
-      </c>
-      <c r="H17">
-        <v>0.4</v>
-      </c>
-      <c r="I17">
-        <v>0.6</v>
-      </c>
-      <c r="J17">
-        <v>1.1</v>
-      </c>
       <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
         <v>1.6</v>
       </c>
-      <c r="L17">
-        <v>2.5</v>
-      </c>
       <c r="M17">
+        <v>2.2</v>
+      </c>
+      <c r="N17">
         <v>3.4</v>
       </c>
-      <c r="N17">
-        <v>4.4</v>
-      </c>
       <c r="O17">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="P17">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="Q17">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="R17">
-        <v>13.9</v>
+        <v>12.8</v>
       </c>
       <c r="S17">
-        <v>18.4</v>
+        <v>19.9</v>
       </c>
       <c r="T17">
-        <v>24.6</v>
+        <v>28.6</v>
       </c>
       <c r="U17">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="V17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -1601,10 +1601,10 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>886.87</v>
+        <v>930.8099999999999</v>
       </c>
       <c r="C18">
-        <v>27.19</v>
+        <v>28.66</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1634,34 +1634,34 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O18">
         <v>0.1</v>
       </c>
       <c r="P18">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q18">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="R18">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="T18">
-        <v>7.7</v>
+        <v>11.7</v>
       </c>
       <c r="U18">
-        <v>52.3</v>
+        <v>61.8</v>
       </c>
       <c r="V18">
-        <v>35.5</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1669,10 +1669,10 @@
         <v>21</v>
       </c>
       <c r="B19">
-        <v>891.86</v>
+        <v>935.33</v>
       </c>
       <c r="C19">
-        <v>24.46</v>
+        <v>23.27</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1714,22 +1714,22 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="S19">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="T19">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="U19">
-        <v>32.3</v>
+        <v>19.2</v>
       </c>
       <c r="V19">
-        <v>62.8</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
